--- a/Phoenix_Suns_2025-26_stats.xlsx
+++ b/Phoenix_Suns_2025-26_stats.xlsx
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>32</v>
@@ -1284,7 +1284,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L14" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -3032,16 +3032,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -3056,7 +3056,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>4</v>
@@ -3077,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.75</v>
+        <v>12.15384615384615</v>
       </c>
     </row>
     <row r="7">
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.833333333333334</v>
+        <v>8.384615384615385</v>
       </c>
     </row>
     <row r="10">
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.444444444444445</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nick Richards</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.25</v>
+        <v>4.538461538461538</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Koby Brea</t>
+          <t>Nick Richards</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>4.230769230769231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Koby Brea</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.25</v>
+        <v>3.230769230769231</v>
       </c>
     </row>
     <row r="6">
@@ -4241,21 +4241,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Dunn</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Ryan Dunn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.666666666666667</v>
+        <v>1.615384615384615</v>
       </c>
     </row>
     <row r="10">
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.416666666666667</v>
+        <v>1.307692307692308</v>
       </c>
     </row>
     <row r="11">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3846153846153846</v>
       </c>
     </row>
     <row r="16">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.727272727272727</v>
+        <v>8.818181818181818</v>
       </c>
     </row>
     <row r="3">
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.666666666666667</v>
+        <v>5.461538461538462</v>
       </c>
     </row>
     <row r="4">
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.333333333333333</v>
+        <v>5.153846153846154</v>
       </c>
     </row>
     <row r="5">
@@ -4417,51 +4417,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nick Richards</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.583333333333333</v>
+        <v>3.461538461538462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.166666666666667</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Nick Richards</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.076923076923077</v>
+        <v>3.384615384615385</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.857142857142857</v>
+        <v>3.076923076923077</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.777777777777778</v>
+        <v>2.857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.583333333333333</v>
+        <v>3.384615384615385</v>
       </c>
     </row>
     <row r="4">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.111111111111111</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="10">
